--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487874_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487874_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.438</v>
+        <v>4.638</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4018</v>
+        <v>5.866</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9637</v>
+        <v>-1.228</v>
       </c>
       <c r="G2" t="n">
         <v>2.287</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7993</v>
+        <v>0.9993</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3197</v>
+        <v>0.784</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4796</v>
+        <v>0.2153</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9376</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9916</v>
+        <v>3.1783</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0098</v>
+        <v>2.6679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9818</v>
+        <v>0.5105</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1869</v>
+        <v>0.673</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3389</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5258</v>
+        <v>1.4981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3234</v>
+        <v>0.665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.245</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0784</v>
+        <v>1.245</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5103</v>
+        <v>0.0081</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0939</v>
+        <v>-0.245</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6041</v>
+        <v>0.2531</v>
       </c>
       <c r="P3" t="n">
         <v>0.8325</v>
@@ -688,22 +688,22 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>2.346</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6864</v>
+        <v>0.8354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6596</v>
+        <v>0.1299</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2379</v>
+        <v>2.4816</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9778</v>
+        <v>2.1921</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2602</v>
+        <v>0.2895</v>
       </c>
       <c r="G4" t="n">
         <v>2.3084</v>
@@ -766,13 +766,13 @@
         <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4867</v>
+        <v>-0.243</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.2143</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4867</v>
+        <v>-0.4573</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0122</v>
+        <v>1.7211</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5311</v>
+        <v>1.0035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4811</v>
+        <v>0.7176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.673</v>
+        <v>-0.1869</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8250999999999999</v>
+        <v>0.3389</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4981</v>
+        <v>-0.5258</v>
       </c>
       <c r="J5" t="n">
-        <v>0.665</v>
+        <v>0.3234</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.245</v>
       </c>
       <c r="L5" t="n">
-        <v>1.245</v>
+        <v>0.0784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0081</v>
+        <v>-0.5103</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.245</v>
+        <v>0.0939</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2531</v>
+        <v>-0.6041</v>
       </c>
       <c r="P5" t="n">
         <v>0.8325</v>
@@ -844,28 +844,28 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2009</v>
+        <v>1.0755</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3014</v>
+        <v>0.6801</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1005</v>
+        <v>0.3954</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2517</v>
+        <v>-0.107</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7212</v>
+        <v>-1.3869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4695</v>
+        <v>1.2798</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3296</v>
+        <v>-1.5113</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0836</v>
+        <v>-1.6909</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4132</v>
+        <v>0.1796</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4442</v>
+        <v>-0.5682</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2139</v>
+        <v>-1.352</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6581</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1146</v>
+        <v>-0.9431</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8697</v>
+        <v>-0.3389</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2449</v>
+        <v>-0.6041</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8754999999999999</v>
+        <v>-0.0109</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9564</v>
+        <v>0.222</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0809</v>
+        <v>-0.2329</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4152</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.4152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4596</v>
+        <v>-0.2475</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8887</v>
+        <v>-0.805</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3483</v>
+        <v>0.5576</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0531</v>
+        <v>0.3296</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2516</v>
+        <v>-1.0836</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1985</v>
+        <v>1.4132</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0005</v>
+        <v>1.4442</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0472</v>
+        <v>-0.2139</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0477</v>
+        <v>1.6581</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0536</v>
+        <v>-1.1146</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2044</v>
+        <v>-0.8697</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8492</v>
+        <v>-0.2449</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3229</v>
+        <v>0.8798</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6582</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3353</v>
+        <v>0.0072</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7602</v>
+        <v>-0.4363</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9226</v>
+        <v>1.912</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1624</v>
+        <v>-2.3483</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5113</v>
+        <v>-2.0531</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6909</v>
+        <v>-3.2516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1796</v>
+        <v>1.1985</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5682</v>
+        <v>1.0005</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.352</v>
+        <v>-2.0472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7838000000000001</v>
+        <v>3.0477</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9431</v>
+        <v>-3.0536</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3389</v>
+        <v>-1.2044</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6041</v>
+        <v>-1.8492</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6642</v>
+        <v>0.3462</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3138</v>
+        <v>0.6815</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3503</v>
+        <v>-0.3353</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4152</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>1.4152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3435</v>
+        <v>-1.5866</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8387</v>
+        <v>1.713</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1822</v>
+        <v>-3.2996</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8152</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4281</v>
+        <v>1.1849</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5155</v>
+        <v>1.3897</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.2048</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7076</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5985</v>
+        <v>-2.6214</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2329</v>
+        <v>-2.1677</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3656</v>
+        <v>-0.4537</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6667</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0587</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.171</v>
+        <v>-0.1057</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1122</v>
+        <v>0.0242</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.436</v>
+        <v>-2.8312</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0354</v>
+        <v>0.464</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4714</v>
+        <v>-3.2952</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1277</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.327</v>
+        <v>-0.7222</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>-0.2891</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6093</v>
+        <v>-0.4332</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8137</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8539</v>
+        <v>-4.4232</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2086</v>
+        <v>-1.0129</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6452</v>
+        <v>-3.4103</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7928</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.291</v>
+        <v>0.1396</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4344</v>
+        <v>0.6301</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7254</v>
+        <v>-0.4906</v>
       </c>
       <c r="V12" t="n">
         <v>0.23</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.0924</v>
+        <v>-7.9032</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6238</v>
+        <v>-5.4934</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4686</v>
+        <v>-2.4099</v>
       </c>
       <c r="G13" t="n">
         <v>-9.426299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2499</v>
+        <v>-0.0607</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2395</v>
+        <v>-0.109</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0104</v>
+        <v>0.0483</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.116099999999999</v>
+        <v>-8.1374</v>
       </c>
       <c r="E14" t="n">
-        <v>3.974199999999999</v>
+        <v>4.952599999999998</v>
       </c>
       <c r="F14" t="n">
         <v>-13.09</v>
@@ -1516,10 +1516,10 @@
         <v>-8.123899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.858199999999999</v>
+        <v>-7.8582</v>
       </c>
       <c r="J14" t="n">
-        <v>7.002300000000002</v>
+        <v>7.002299999999998</v>
       </c>
       <c r="K14" t="n">
         <v>2.961100000000001</v>
@@ -1546,10 +1546,10 @@
         <v>13.5277</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4934</v>
+        <v>4.4721</v>
       </c>
       <c r="T14" t="n">
-        <v>4.8272</v>
+        <v>5.805800000000001</v>
       </c>
       <c r="U14" t="n">
         <v>-1.3338</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.976</v>
+        <v>7.8714</v>
       </c>
       <c r="E15" t="n">
-        <v>4.742</v>
+        <v>5.3849</v>
       </c>
       <c r="F15" t="n">
-        <v>2.234</v>
+        <v>2.4865</v>
       </c>
       <c r="G15" t="n">
         <v>8.463100000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2165</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.64</v>
+        <v>0.0029</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4235</v>
+        <v>0.676</v>
       </c>
       <c r="V15" t="n">
         <v>-0.23</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8604</v>
+        <v>5.8785</v>
       </c>
       <c r="E16" t="n">
-        <v>7.6989</v>
+        <v>7.1631</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8385</v>
+        <v>-1.2846</v>
       </c>
       <c r="G16" t="n">
         <v>4.9558</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6746</v>
+        <v>0.6927</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0497</v>
+        <v>0.5139</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3751</v>
+        <v>0.1788</v>
       </c>
       <c r="V16" t="n">
         <v>0.23</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5946</v>
+        <v>5.7003</v>
       </c>
       <c r="E17" t="n">
         <v>2.6056</v>
       </c>
       <c r="F17" t="n">
-        <v>2.989</v>
+        <v>3.0947</v>
       </c>
       <c r="G17" t="n">
         <v>4.8903</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9343</v>
+        <v>1.04</v>
       </c>
       <c r="T17" t="n">
         <v>0.1396</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7947</v>
+        <v>0.9004</v>
       </c>
       <c r="V17" t="n">
         <v>-0.23</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5828</v>
+        <v>3.832</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1287</v>
+        <v>3.0869</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4541</v>
+        <v>0.7451</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4619</v>
+        <v>0.8474</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2388</v>
+        <v>0.3519</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7007</v>
+        <v>0.4956</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3806</v>
+        <v>1.7661</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0104</v>
+        <v>0.7439</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3702</v>
+        <v>1.0221</v>
       </c>
       <c r="M18" t="n">
         <v>-0.9186</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2492</v>
+        <v>-0.3921</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6694</v>
+        <v>-0.5266</v>
       </c>
       <c r="P18" t="n">
         <v>0.4162</v>
@@ -1858,19 +1858,19 @@
         <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7046</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9968</v>
+        <v>0.8182</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2922</v>
+        <v>-0.0012</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5486</v>
+        <v>3.5368</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4083</v>
+        <v>2.9144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1403</v>
+        <v>0.6224</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8474</v>
+        <v>2.4619</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3519</v>
+        <v>-0.2388</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4956</v>
+        <v>2.7007</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7661</v>
+        <v>3.3806</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7439</v>
+        <v>0.0104</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0221</v>
+        <v>3.3702</v>
       </c>
       <c r="M19" t="n">
         <v>-0.9186</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3921</v>
+        <v>-0.2492</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5266</v>
+        <v>-0.6694</v>
       </c>
       <c r="P19" t="n">
         <v>0.4162</v>
@@ -1936,19 +1936,19 @@
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5337</v>
+        <v>0.6586</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1397</v>
+        <v>0.7825</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.606</v>
+        <v>-0.1239</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6648</v>
+        <v>1.976</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2475</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9123</v>
+        <v>2.2235</v>
       </c>
       <c r="G20" t="n">
         <v>1.9892</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9727</v>
+        <v>-0.6615</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5748</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3979</v>
+        <v>-0.0867</v>
       </c>
       <c r="V20" t="n">
         <v>2.1051</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9727</v>
+        <v>-1.2585</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1213</v>
+        <v>1.6927</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.094</v>
+        <v>-2.9511</v>
       </c>
       <c r="G21" t="n">
         <v>0.5366</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5063</v>
+        <v>-0.792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2701</v>
+        <v>-0.1586</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7763</v>
+        <v>-0.6334</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6275</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0091</v>
+        <v>-2.3726</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6479</v>
+        <v>-2.3264</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3612</v>
+        <v>-0.0461</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7495000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.552</v>
+        <v>-0.9155</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1881</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0425</v>
+        <v>-0.7274</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7076</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3337</v>
+        <v>-6.0646</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0366</v>
+        <v>-2.8223</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2971</v>
+        <v>-3.2423</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9521</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2141</v>
+        <v>-0.945</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2362</v>
+        <v>-0.0219</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9779</v>
+        <v>-0.9231</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7956</v>
+        <v>-7.1257</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6827</v>
+        <v>-4.3612</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1129</v>
+        <v>-2.7645</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4609</v>
@@ -2326,13 +2326,13 @@
         <v>1.0406</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8789</v>
+        <v>-1.2091</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3014</v>
+        <v>0.02</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5775</v>
+        <v>-1.2291</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4152</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.116100000000003</v>
+        <v>11.9736</v>
       </c>
       <c r="E25" t="n">
-        <v>13.0901</v>
+        <v>13.0902</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.974</v>
+        <v>-1.116400000000001</v>
       </c>
       <c r="G25" t="n">
         <v>15.9818</v>
       </c>
       <c r="H25" t="n">
-        <v>8.123800000000003</v>
+        <v>8.123800000000001</v>
       </c>
       <c r="I25" t="n">
         <v>7.8582</v>
@@ -2404,13 +2404,13 @@
         <v>11.4465</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4933</v>
+        <v>-0.6358999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3339</v>
+        <v>1.3337</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.8272</v>
+        <v>-1.9696</v>
       </c>
       <c r="V25" t="n">
         <v>-1.291399999999999</v>
